--- a/artfynd/A 58632-2024 artfynd.xlsx
+++ b/artfynd/A 58632-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2859617</v>
+        <v>68386980</v>
       </c>
       <c r="B2" t="n">
-        <v>96311</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandbol, 400 m N om, Dls</t>
+          <t>Sandbol, SANDBOL, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>357494.3512045676</v>
+        <v>357439</v>
       </c>
       <c r="R2" t="n">
-        <v>6536316.203818563</v>
+        <v>6536287</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1978-08-18</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1978-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,18 +761,129 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vid en av Trafikverkets Artrika vägkanter.</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Johanna Borlid</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mats Lindqvist</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2859617</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sandbol, 400 m N om, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>357494</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6536316</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ånimskog</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1978-08-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1978-08-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Kjell Eriksson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Kjell Eriksson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
